--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/22.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/22.xlsx
@@ -426,13 +426,13 @@
         <v>-9.704847235143063</v>
       </c>
       <c r="E2">
-        <v>-12.39209298025016</v>
+        <v>-8.200962836025933</v>
       </c>
       <c r="F2">
-        <v>3.581506789576559</v>
+        <v>3.897800658252689</v>
       </c>
       <c r="G2">
-        <v>-19.03515626681124</v>
+        <v>-19.64643078388533</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.133641205208097</v>
       </c>
       <c r="E3">
-        <v>-11.24382141958421</v>
+        <v>-9.557243832684591</v>
       </c>
       <c r="F3">
-        <v>3.810555346655039</v>
+        <v>3.747234942385045</v>
       </c>
       <c r="G3">
-        <v>-18.49939492629052</v>
+        <v>-18.87532191414025</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.397776220444014</v>
       </c>
       <c r="E4">
-        <v>-12.0525471883888</v>
+        <v>-10.10162600708649</v>
       </c>
       <c r="F4">
-        <v>3.334978023564204</v>
+        <v>3.43901765588621</v>
       </c>
       <c r="G4">
-        <v>-18.13377581077265</v>
+        <v>-18.56779447651925</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.610733104191524</v>
       </c>
       <c r="E5">
-        <v>-12.2566899846381</v>
+        <v>-10.6507428423987</v>
       </c>
       <c r="F5">
-        <v>4.185656673990711</v>
+        <v>3.455225492489386</v>
       </c>
       <c r="G5">
-        <v>-17.34244476611096</v>
+        <v>-17.70027080902436</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.804611480121073</v>
       </c>
       <c r="E6">
-        <v>-13.8377137057172</v>
+        <v>-10.89354788287083</v>
       </c>
       <c r="F6">
-        <v>4.044433285691841</v>
+        <v>3.713416014798352</v>
       </c>
       <c r="G6">
-        <v>-16.37735692056003</v>
+        <v>-16.64615918366105</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.045336067910481</v>
       </c>
       <c r="E7">
-        <v>-14.79858406498424</v>
+        <v>-12.24502776723798</v>
       </c>
       <c r="F7">
-        <v>3.843287456209259</v>
+        <v>3.797823339674011</v>
       </c>
       <c r="G7">
-        <v>-16.1850259772773</v>
+        <v>-16.12106404016732</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.365889668821847</v>
       </c>
       <c r="E8">
-        <v>-15.51849756281869</v>
+        <v>-12.69029355337285</v>
       </c>
       <c r="F8">
-        <v>3.524094301623331</v>
+        <v>3.925854148715897</v>
       </c>
       <c r="G8">
-        <v>-14.88778615112198</v>
+        <v>-15.59633179017176</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-4.799073318460123</v>
       </c>
       <c r="E9">
-        <v>-15.30834506978237</v>
+        <v>-13.11874714006481</v>
       </c>
       <c r="F9">
-        <v>4.214352977558492</v>
+        <v>3.754083884071391</v>
       </c>
       <c r="G9">
-        <v>-15.79986935461184</v>
+        <v>-15.22634098283607</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.356160228567311</v>
       </c>
       <c r="E10">
-        <v>-16.64521395670878</v>
+        <v>-13.66104855559297</v>
       </c>
       <c r="F10">
-        <v>4.182671237871022</v>
+        <v>3.830053458582134</v>
       </c>
       <c r="G10">
-        <v>-14.4859468705193</v>
+        <v>-14.40059771371892</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.034455752069396</v>
       </c>
       <c r="E11">
-        <v>-15.44787220423998</v>
+        <v>-14.36679960280976</v>
       </c>
       <c r="F11">
-        <v>4.130288596787592</v>
+        <v>4.474230055899558</v>
       </c>
       <c r="G11">
-        <v>-13.79810182533245</v>
+        <v>-14.01255099679109</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.826302290761996</v>
       </c>
       <c r="E12">
-        <v>-17.86312656486945</v>
+        <v>-14.4590922648701</v>
       </c>
       <c r="F12">
-        <v>4.782397640354225</v>
+        <v>4.691987965277881</v>
       </c>
       <c r="G12">
-        <v>-13.07362150667081</v>
+        <v>-13.67709381353435</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.703394521006007</v>
       </c>
       <c r="E13">
-        <v>-18.76517914535426</v>
+        <v>-15.53085751972138</v>
       </c>
       <c r="F13">
-        <v>5.430330055475942</v>
+        <v>4.586167343039856</v>
       </c>
       <c r="G13">
-        <v>-12.99892027168529</v>
+        <v>-13.13891231277767</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.64727851836115</v>
       </c>
       <c r="E14">
-        <v>-18.05681157500283</v>
+        <v>-15.78872210445734</v>
       </c>
       <c r="F14">
-        <v>5.222610302284743</v>
+        <v>4.55390408943562</v>
       </c>
       <c r="G14">
-        <v>-11.86337169029138</v>
+        <v>-12.92593168515153</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.620878870678095</v>
       </c>
       <c r="E15">
-        <v>-20.54437334479756</v>
+        <v>-17.67962107569322</v>
       </c>
       <c r="F15">
-        <v>4.974187888389589</v>
+        <v>4.824947560366424</v>
       </c>
       <c r="G15">
-        <v>-12.33776878457028</v>
+        <v>-12.63061208923857</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.60342733445661</v>
       </c>
       <c r="E16">
-        <v>-20.67437716568734</v>
+        <v>-18.11112727270893</v>
       </c>
       <c r="F16">
-        <v>5.199538613381971</v>
+        <v>5.297715061226963</v>
       </c>
       <c r="G16">
-        <v>-11.28136753620057</v>
+        <v>-12.40623817221682</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-3.566403848043035</v>
       </c>
       <c r="E17">
-        <v>-20.31480874202898</v>
+        <v>-18.63341436286275</v>
       </c>
       <c r="F17">
-        <v>5.79265630072564</v>
+        <v>5.540212991457296</v>
       </c>
       <c r="G17">
-        <v>-11.35681022264997</v>
+        <v>-12.50338397845214</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.496569669853301</v>
       </c>
       <c r="E18">
-        <v>-20.67502091344269</v>
+        <v>-20.3543888459546</v>
       </c>
       <c r="F18">
-        <v>5.62023659603734</v>
+        <v>5.646858667628511</v>
       </c>
       <c r="G18">
-        <v>-10.88795965525489</v>
+        <v>-11.95286018264097</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.379244019097012</v>
       </c>
       <c r="E19">
-        <v>-23.28388967961301</v>
+        <v>-21.65277822995647</v>
       </c>
       <c r="F19">
-        <v>6.188175227805514</v>
+        <v>5.769745315099011</v>
       </c>
       <c r="G19">
-        <v>-10.74709040397989</v>
+        <v>-11.589444535558</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.211580438488459</v>
       </c>
       <c r="E20">
-        <v>-23.59879031547284</v>
+        <v>-21.43205996730979</v>
       </c>
       <c r="F20">
-        <v>6.106720204353434</v>
+        <v>6.083100136230009</v>
       </c>
       <c r="G20">
-        <v>-10.59610321204204</v>
+        <v>-12.1921362297888</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.99355747520895</v>
       </c>
       <c r="E21">
-        <v>-22.84405629389102</v>
+        <v>-21.93771759931899</v>
       </c>
       <c r="F21">
-        <v>6.358432893572508</v>
+        <v>6.135555673644885</v>
       </c>
       <c r="G21">
-        <v>-10.65117947993616</v>
+        <v>-11.00353079144199</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.732155050575044</v>
       </c>
       <c r="E22">
-        <v>-24.08552176347479</v>
+        <v>-22.69600261658353</v>
       </c>
       <c r="F22">
-        <v>6.236316627786611</v>
+        <v>6.272496402471281</v>
       </c>
       <c r="G22">
-        <v>-10.88393780321228</v>
+        <v>-11.21462646147335</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.437956647051823</v>
       </c>
       <c r="E23">
-        <v>-25.14731515793516</v>
+        <v>-22.80798150032356</v>
       </c>
       <c r="F23">
-        <v>6.751920663780719</v>
+        <v>6.135081847490483</v>
       </c>
       <c r="G23">
-        <v>-10.67829728400406</v>
+        <v>-10.81515512621481</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.121984147861514</v>
       </c>
       <c r="E24">
-        <v>-25.81795495661185</v>
+        <v>-23.86740341111745</v>
       </c>
       <c r="F24">
-        <v>6.587343941662124</v>
+        <v>6.444482042640515</v>
       </c>
       <c r="G24">
-        <v>-9.000729407304529</v>
+        <v>-10.81366700179787</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.797438211284798</v>
       </c>
       <c r="E25">
-        <v>-25.8700528394705</v>
+        <v>-24.27134059135895</v>
       </c>
       <c r="F25">
-        <v>5.977417022980847</v>
+        <v>6.077699180763756</v>
       </c>
       <c r="G25">
-        <v>-9.663123608844906</v>
+        <v>-10.6642997768788</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.47209423809297</v>
       </c>
       <c r="E26">
-        <v>-25.46377740125312</v>
+        <v>-25.02855408010169</v>
       </c>
       <c r="F26">
-        <v>6.744806644525476</v>
+        <v>6.008248857713046</v>
       </c>
       <c r="G26">
-        <v>-9.620008467294966</v>
+        <v>-10.72307155374165</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.156070006779458</v>
       </c>
       <c r="E27">
-        <v>-25.35765869869242</v>
+        <v>-24.92282993261685</v>
       </c>
       <c r="F27">
-        <v>6.269192873268917</v>
+        <v>6.40318792761096</v>
       </c>
       <c r="G27">
-        <v>-9.789825654596225</v>
+        <v>-9.687296493014024</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.8520210821970804</v>
       </c>
       <c r="E28">
-        <v>-27.17166511546043</v>
+        <v>-25.76815379961583</v>
       </c>
       <c r="F28">
-        <v>6.167272204763272</v>
+        <v>6.049282865378122</v>
       </c>
       <c r="G28">
-        <v>-8.75113308678803</v>
+        <v>-9.876794778415391</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.5677762437393876</v>
       </c>
       <c r="E29">
-        <v>-27.2150329481143</v>
+        <v>-26.44435474825646</v>
       </c>
       <c r="F29">
-        <v>6.030788734743219</v>
+        <v>5.85358437993635</v>
       </c>
       <c r="G29">
-        <v>-8.3780407148781</v>
+        <v>-9.596009197641157</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.3055619896882673</v>
       </c>
       <c r="E30">
-        <v>-27.27073997161422</v>
+        <v>-26.34504731226849</v>
       </c>
       <c r="F30">
-        <v>6.051451531238651</v>
+        <v>5.780379895816152</v>
       </c>
       <c r="G30">
-        <v>-8.891035057192019</v>
+        <v>-9.255130803240974</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-0.07336461294108351</v>
       </c>
       <c r="E31">
-        <v>-26.90995881024902</v>
+        <v>-27.33322918920759</v>
       </c>
       <c r="F31">
-        <v>5.846854723156007</v>
+        <v>5.58366086173413</v>
       </c>
       <c r="G31">
-        <v>-8.962621673880346</v>
+        <v>-8.69545895838254</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.1244632404368879</v>
       </c>
       <c r="E32">
-        <v>-27.79998369073712</v>
+        <v>-26.66516438155229</v>
       </c>
       <c r="F32">
-        <v>5.951621662057671</v>
+        <v>5.53798302640896</v>
       </c>
       <c r="G32">
-        <v>-8.542118180195796</v>
+        <v>-8.49882289726907</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.2795634434161439</v>
       </c>
       <c r="E33">
-        <v>-27.66657423656098</v>
+        <v>-27.86631878201728</v>
       </c>
       <c r="F33">
-        <v>6.674988526347923</v>
+        <v>5.687569612006495</v>
       </c>
       <c r="G33">
-        <v>-7.773558049857799</v>
+        <v>-8.93669698009059</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.3866582571801098</v>
       </c>
       <c r="E34">
-        <v>-28.27820105552318</v>
+        <v>-27.4395513991232</v>
       </c>
       <c r="F34">
-        <v>5.406658628573544</v>
+        <v>5.73644163203686</v>
       </c>
       <c r="G34">
-        <v>-8.741051696549448</v>
+        <v>-8.167494606583178</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.4384649209523228</v>
       </c>
       <c r="E35">
-        <v>-25.55390624021322</v>
+        <v>-27.10960367863352</v>
       </c>
       <c r="F35">
-        <v>5.68434891954441</v>
+        <v>5.964358639243116</v>
       </c>
       <c r="G35">
-        <v>-7.819789115077233</v>
+        <v>-7.916876179559258</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.4328715024239766</v>
       </c>
       <c r="E36">
-        <v>-26.11408723049477</v>
+        <v>-26.47938293257006</v>
       </c>
       <c r="F36">
-        <v>6.047324604837904</v>
+        <v>5.906570072489017</v>
       </c>
       <c r="G36">
-        <v>-7.774948271352567</v>
+        <v>-7.769148502243409</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.3684769414090233</v>
       </c>
       <c r="E37">
-        <v>-25.96854624603881</v>
+        <v>-26.50398655645835</v>
       </c>
       <c r="F37">
-        <v>6.035980941623967</v>
+        <v>5.672357473021485</v>
       </c>
       <c r="G37">
-        <v>-8.966159232801303</v>
+        <v>-7.861856042673842</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.249794691098864</v>
       </c>
       <c r="E38">
-        <v>-25.37906850307191</v>
+        <v>-26.86288215988208</v>
       </c>
       <c r="F38">
-        <v>6.25087766999302</v>
+        <v>5.815863841882472</v>
       </c>
       <c r="G38">
-        <v>-8.669398505874048</v>
+        <v>-8.015281670059796</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.08247401683797137</v>
       </c>
       <c r="E39">
-        <v>-25.95366528986195</v>
+        <v>-27.39507881225694</v>
       </c>
       <c r="F39">
-        <v>6.875851054178747</v>
+        <v>6.109369323307586</v>
       </c>
       <c r="G39">
-        <v>-8.370200648870988</v>
+        <v>-7.87084614167334</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.1246092327040349</v>
       </c>
       <c r="E40">
-        <v>-25.33966283402194</v>
+        <v>-26.14325938684037</v>
       </c>
       <c r="F40">
-        <v>6.419983905070123</v>
+        <v>6.164929581748155</v>
       </c>
       <c r="G40">
-        <v>-8.565212826848786</v>
+        <v>-7.780463469301294</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.3626858656535688</v>
       </c>
       <c r="E41">
-        <v>-24.46473072348826</v>
+        <v>-25.78608736611644</v>
       </c>
       <c r="F41">
-        <v>6.881015096567799</v>
+        <v>6.496975684955919</v>
       </c>
       <c r="G41">
-        <v>-8.820889571517988</v>
+        <v>-8.065256543022887</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.6233382915326982</v>
       </c>
       <c r="E42">
-        <v>-24.62644015963179</v>
+        <v>-25.91464586946518</v>
       </c>
       <c r="F42">
-        <v>7.00250511659718</v>
+        <v>6.801435496915656</v>
       </c>
       <c r="G42">
-        <v>-8.40503059246103</v>
+        <v>-7.802123511801465</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.898720427577681</v>
       </c>
       <c r="E43">
-        <v>-24.99223424706606</v>
+        <v>-26.19755431848985</v>
       </c>
       <c r="F43">
-        <v>6.558364336442586</v>
+        <v>6.654960259283036</v>
       </c>
       <c r="G43">
-        <v>-8.919954275027781</v>
+        <v>-8.507375696549557</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.183524335456584</v>
       </c>
       <c r="E44">
-        <v>-22.10986820873313</v>
+        <v>-25.61266172082557</v>
       </c>
       <c r="F44">
-        <v>7.068530968804717</v>
+        <v>6.619125085437929</v>
       </c>
       <c r="G44">
-        <v>-8.0017958688744</v>
+        <v>-8.74412976442237</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.471714203471585</v>
       </c>
       <c r="E45">
-        <v>-24.59197681205836</v>
+        <v>-24.4849444030062</v>
       </c>
       <c r="F45">
-        <v>6.832646723918335</v>
+        <v>6.97111330550069</v>
       </c>
       <c r="G45">
-        <v>-9.624684310857649</v>
+        <v>-8.967528568339343</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.760231251745295</v>
       </c>
       <c r="E46">
-        <v>-23.9804912022812</v>
+        <v>-24.6564014261291</v>
       </c>
       <c r="F46">
-        <v>6.983987791674999</v>
+        <v>6.690686088630973</v>
       </c>
       <c r="G46">
-        <v>-9.516055144538313</v>
+        <v>-9.002036084972383</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.042659748948674</v>
       </c>
       <c r="E47">
-        <v>-23.01042978635233</v>
+        <v>-23.32464929555488</v>
       </c>
       <c r="F47">
-        <v>6.868596212465029</v>
+        <v>7.265071075527733</v>
       </c>
       <c r="G47">
-        <v>-9.906405843567798</v>
+        <v>-8.994902225377166</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.31713336970976</v>
       </c>
       <c r="E48">
-        <v>-22.30098238105644</v>
+        <v>-23.48169052216929</v>
       </c>
       <c r="F48">
-        <v>6.804621397946823</v>
+        <v>7.119962644109733</v>
       </c>
       <c r="G48">
-        <v>-10.62049278801222</v>
+        <v>-9.529469150247452</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.576775576510104</v>
       </c>
       <c r="E49">
-        <v>-21.89419609784611</v>
+        <v>-22.49861294194841</v>
       </c>
       <c r="F49">
-        <v>6.831909476929844</v>
+        <v>7.175343975191296</v>
       </c>
       <c r="G49">
-        <v>-9.925002177290297</v>
+        <v>-9.026876014384531</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.821487765104124</v>
       </c>
       <c r="E50">
-        <v>-21.74464726446168</v>
+        <v>-22.82056157742646</v>
       </c>
       <c r="F50">
-        <v>6.432608224288787</v>
+        <v>7.309524583831566</v>
       </c>
       <c r="G50">
-        <v>-10.43414567133232</v>
+        <v>-9.608692194864785</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.044716932977402</v>
       </c>
       <c r="E51">
-        <v>-19.90009813161088</v>
+        <v>-23.01805508234471</v>
       </c>
       <c r="F51">
-        <v>6.964772981399662</v>
+        <v>7.144074762470421</v>
       </c>
       <c r="G51">
-        <v>-9.705267553406953</v>
+        <v>-9.580184169302123</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.247012138666002</v>
       </c>
       <c r="E52">
-        <v>-20.22652808210843</v>
+        <v>-21.96489621422866</v>
       </c>
       <c r="F52">
-        <v>6.940665833243391</v>
+        <v>7.357140798879287</v>
       </c>
       <c r="G52">
-        <v>-11.27981283779656</v>
+        <v>-10.03444067443288</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.424255032700763</v>
       </c>
       <c r="E53">
-        <v>-21.76225272726763</v>
+        <v>-21.76614843949032</v>
       </c>
       <c r="F53">
-        <v>6.489005133806183</v>
+        <v>7.151390903371946</v>
       </c>
       <c r="G53">
-        <v>-11.17803165453971</v>
+        <v>-10.67222860820201</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.577298056776309</v>
       </c>
       <c r="E54">
-        <v>-19.53106869255457</v>
+        <v>-20.90052367553558</v>
       </c>
       <c r="F54">
-        <v>6.593621309840538</v>
+        <v>7.469248729704561</v>
       </c>
       <c r="G54">
-        <v>-10.83337290197159</v>
+        <v>-10.67500121895778</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.706362247695139</v>
       </c>
       <c r="E55">
-        <v>-19.69033604043909</v>
+        <v>-21.05974118488421</v>
       </c>
       <c r="F55">
-        <v>6.902383662090415</v>
+        <v>7.455552503066674</v>
       </c>
       <c r="G55">
-        <v>-10.42302781549107</v>
+        <v>-10.38678023758805</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.813099972102357</v>
       </c>
       <c r="E56">
-        <v>-18.57489561529591</v>
+        <v>-20.28419126814235</v>
       </c>
       <c r="F56">
-        <v>6.822459461598707</v>
+        <v>7.185821166101904</v>
       </c>
       <c r="G56">
-        <v>-10.84962348167898</v>
+        <v>-10.59099790099411</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.901975213755455</v>
       </c>
       <c r="E57">
-        <v>-19.37726697077352</v>
+        <v>-20.42481900360104</v>
       </c>
       <c r="F57">
-        <v>6.771490015304454</v>
+        <v>7.474532056999617</v>
       </c>
       <c r="G57">
-        <v>-11.06517830347195</v>
+        <v>-11.00427876976735</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.974385479557902</v>
       </c>
       <c r="E58">
-        <v>-18.91557108063762</v>
+        <v>-19.97832386691402</v>
       </c>
       <c r="F58">
-        <v>7.541172557820031</v>
+        <v>7.491178928326275</v>
       </c>
       <c r="G58">
-        <v>-12.21442285099084</v>
+        <v>-11.55745899819998</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.037554039286967</v>
       </c>
       <c r="E59">
-        <v>-18.16007286817204</v>
+        <v>-18.98779542557639</v>
       </c>
       <c r="F59">
-        <v>7.05165381134008</v>
+        <v>7.812098400579638</v>
       </c>
       <c r="G59">
-        <v>-11.0475375022698</v>
+        <v>-11.30016489725658</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.091961253738801</v>
       </c>
       <c r="E60">
-        <v>-17.84714500769151</v>
+        <v>-18.97421857775553</v>
       </c>
       <c r="F60">
-        <v>7.242141865818243</v>
+        <v>7.806660996947661</v>
       </c>
       <c r="G60">
-        <v>-11.91441566316453</v>
+        <v>-11.53540864938343</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.145435365281129</v>
       </c>
       <c r="E61">
-        <v>-18.26622064321201</v>
+        <v>-18.35759959878088</v>
       </c>
       <c r="F61">
-        <v>7.636733021406982</v>
+        <v>7.760131599932413</v>
       </c>
       <c r="G61">
-        <v>-11.61167372037904</v>
+        <v>-11.51965019503148</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.19671654747991</v>
       </c>
       <c r="E62">
-        <v>-17.27605768447096</v>
+        <v>-18.83647317095626</v>
       </c>
       <c r="F62">
-        <v>7.353757746406254</v>
+        <v>7.608760710949248</v>
       </c>
       <c r="G62">
-        <v>-12.05869846299241</v>
+        <v>-11.59751826320602</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.253390151092259</v>
       </c>
       <c r="E63">
-        <v>-16.77044989099766</v>
+        <v>-18.19581540483351</v>
       </c>
       <c r="F63">
-        <v>6.991438128095778</v>
+        <v>7.875266385247516</v>
       </c>
       <c r="G63">
-        <v>-11.83944029999694</v>
+        <v>-11.29235616018456</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.312813439951241</v>
       </c>
       <c r="E64">
-        <v>-16.66084664413543</v>
+        <v>-17.804420922793</v>
       </c>
       <c r="F64">
-        <v>7.32144147728824</v>
+        <v>7.636113402589688</v>
       </c>
       <c r="G64">
-        <v>-12.29182620662817</v>
+        <v>-12.12300632376071</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.381472199184526</v>
       </c>
       <c r="E65">
-        <v>-15.81058876208256</v>
+        <v>-18.28597746948422</v>
       </c>
       <c r="F65">
-        <v>6.646287252575725</v>
+        <v>7.842739710809191</v>
       </c>
       <c r="G65">
-        <v>-11.99792685577277</v>
+        <v>-11.94794023445902</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.456077910434193</v>
       </c>
       <c r="E66">
-        <v>-15.68696842699904</v>
+        <v>-17.24727177677857</v>
       </c>
       <c r="F66">
-        <v>6.60012565068732</v>
+        <v>7.908286766657911</v>
       </c>
       <c r="G66">
-        <v>-11.79455376824193</v>
+        <v>-11.97665059272749</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.539672284944227</v>
       </c>
       <c r="E67">
-        <v>-17.14263577066084</v>
+        <v>-17.68475444489071</v>
       </c>
       <c r="F67">
-        <v>7.601239134931829</v>
+        <v>7.943139496763297</v>
       </c>
       <c r="G67">
-        <v>-12.06550859025833</v>
+        <v>-12.48429682474651</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.63030851624858</v>
       </c>
       <c r="E68">
-        <v>-16.84344258003152</v>
+        <v>-18.39870393126271</v>
       </c>
       <c r="F68">
-        <v>7.1138575763511</v>
+        <v>7.786496877628716</v>
       </c>
       <c r="G68">
-        <v>-12.37272665464529</v>
+        <v>-12.30046907659704</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.727836720076228</v>
       </c>
       <c r="E69">
-        <v>-15.47851875060589</v>
+        <v>-17.00717463009023</v>
       </c>
       <c r="F69">
-        <v>6.656052047519926</v>
+        <v>7.96264589236442</v>
       </c>
       <c r="G69">
-        <v>-12.65746751347506</v>
+        <v>-12.59979877620196</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.834463845206868</v>
       </c>
       <c r="E70">
-        <v>-16.67284942486419</v>
+        <v>-16.56693838286973</v>
       </c>
       <c r="F70">
-        <v>7.156662633523363</v>
+        <v>8.368052212764109</v>
       </c>
       <c r="G70">
-        <v>-12.16532779895495</v>
+        <v>-12.01638482003194</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.947312727296951</v>
       </c>
       <c r="E71">
-        <v>-16.32007150172193</v>
+        <v>-17.53142203598937</v>
       </c>
       <c r="F71">
-        <v>7.402435928464365</v>
+        <v>8.070290579623411</v>
       </c>
       <c r="G71">
-        <v>-11.75501665215411</v>
+        <v>-13.08414019662841</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.070453221825054</v>
       </c>
       <c r="E72">
-        <v>-16.631433601533</v>
+        <v>-16.44042325949281</v>
       </c>
       <c r="F72">
-        <v>7.350581785783921</v>
+        <v>8.254259382641541</v>
       </c>
       <c r="G72">
-        <v>-12.49773693790157</v>
+        <v>-12.53855201346673</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.197810383412252</v>
       </c>
       <c r="E73">
-        <v>-15.94107435548602</v>
+        <v>-17.44780958559792</v>
       </c>
       <c r="F73">
-        <v>7.108565965382017</v>
+        <v>7.970407694928651</v>
       </c>
       <c r="G73">
-        <v>-11.59740077969942</v>
+        <v>-12.87194279237961</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.333156172505048</v>
       </c>
       <c r="E74">
-        <v>-17.34480579153085</v>
+        <v>-16.92650680652809</v>
       </c>
       <c r="F74">
-        <v>7.127234053171507</v>
+        <v>7.898941125619526</v>
       </c>
       <c r="G74">
-        <v>-12.85610209957303</v>
+        <v>-12.79505636417132</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.468181946923449</v>
       </c>
       <c r="E75">
-        <v>-17.30775914651338</v>
+        <v>-16.71984716421595</v>
       </c>
       <c r="F75">
-        <v>6.249224248657033</v>
+        <v>8.072502320588885</v>
       </c>
       <c r="G75">
-        <v>-12.6177946386685</v>
+        <v>-13.16156182747787</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.606488627940445</v>
       </c>
       <c r="E76">
-        <v>-17.23430960423378</v>
+        <v>-17.38486766797014</v>
       </c>
       <c r="F76">
-        <v>6.732772122897605</v>
+        <v>7.927143722215239</v>
       </c>
       <c r="G76">
-        <v>-13.44797747896284</v>
+        <v>-13.01015038954396</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.738837518776533</v>
       </c>
       <c r="E77">
-        <v>-17.15316831458061</v>
+        <v>-18.50486001272533</v>
       </c>
       <c r="F77">
-        <v>6.526977495550512</v>
+        <v>7.857411754247576</v>
       </c>
       <c r="G77">
-        <v>-12.1869356265633</v>
+        <v>-12.71464543076503</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.868974725281737</v>
       </c>
       <c r="E78">
-        <v>-17.68806040110528</v>
+        <v>-18.57264457475786</v>
       </c>
       <c r="F78">
-        <v>6.62020527653118</v>
+        <v>8.117825614665657</v>
       </c>
       <c r="G78">
-        <v>-12.19025127219402</v>
+        <v>-12.20497848243249</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.988177633517505</v>
       </c>
       <c r="E79">
-        <v>-19.28572603996297</v>
+        <v>-18.59577380862583</v>
       </c>
       <c r="F79">
-        <v>6.686759627141703</v>
+        <v>7.995195761090024</v>
       </c>
       <c r="G79">
-        <v>-11.89070096467115</v>
+        <v>-12.65736047294682</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.100810161460317</v>
       </c>
       <c r="E80">
-        <v>-17.90664806634232</v>
+        <v>-18.30428897821539</v>
       </c>
       <c r="F80">
-        <v>7.124606471769827</v>
+        <v>7.956179656418167</v>
       </c>
       <c r="G80">
-        <v>-11.5666775373512</v>
+        <v>-12.20470043813353</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.202013461613113</v>
       </c>
       <c r="E81">
-        <v>-18.01895920698834</v>
+        <v>-19.69707670241928</v>
       </c>
       <c r="F81">
-        <v>7.022506875905177</v>
+        <v>7.976771213316956</v>
       </c>
       <c r="G81">
-        <v>-12.00662977286725</v>
+        <v>-11.94104786873848</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.294059138978294</v>
       </c>
       <c r="E82">
-        <v>-20.40370407722562</v>
+        <v>-20.70212061733719</v>
       </c>
       <c r="F82">
-        <v>6.776084140920379</v>
+        <v>8.091616070041081</v>
       </c>
       <c r="G82">
-        <v>-12.06558038573458</v>
+        <v>-12.23974837889693</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-6.376684813364741</v>
       </c>
       <c r="E83">
-        <v>-20.25844135792841</v>
+        <v>-20.86924168783697</v>
       </c>
       <c r="F83">
-        <v>6.317272974062206</v>
+        <v>7.942220008946189</v>
       </c>
       <c r="G83">
-        <v>-11.0483311686255</v>
+        <v>-12.30628189942916</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-6.448618181077197</v>
       </c>
       <c r="E84">
-        <v>-22.08869098418783</v>
+        <v>-22.66256926541866</v>
       </c>
       <c r="F84">
-        <v>6.815285799890463</v>
+        <v>7.935752116265131</v>
       </c>
       <c r="G84">
-        <v>-10.23330500605487</v>
+        <v>-11.89479591756232</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.51369716427871</v>
       </c>
       <c r="E85">
-        <v>-22.8752676769971</v>
+        <v>-22.51189075855388</v>
       </c>
       <c r="F85">
-        <v>7.171173973685604</v>
+        <v>8.18948436521223</v>
       </c>
       <c r="G85">
-        <v>-11.63769109560178</v>
+        <v>-11.72997700078074</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.567509329557085</v>
       </c>
       <c r="E86">
-        <v>-23.94578696845094</v>
+        <v>-23.80826998827454</v>
       </c>
       <c r="F86">
-        <v>6.650213714064995</v>
+        <v>8.285510371279555</v>
       </c>
       <c r="G86">
-        <v>-11.4860055294858</v>
+        <v>-12.19268448615293</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.616650355062883</v>
       </c>
       <c r="E87">
-        <v>-25.19877759946111</v>
+        <v>-24.86772927797035</v>
       </c>
       <c r="F87">
-        <v>6.799241980033043</v>
+        <v>7.947395648478881</v>
       </c>
       <c r="G87">
-        <v>-11.74596258991213</v>
+        <v>-12.02657325079876</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.655032729576818</v>
       </c>
       <c r="E88">
-        <v>-26.38057803515239</v>
+        <v>-26.25081094730812</v>
       </c>
       <c r="F88">
-        <v>6.896772301303851</v>
+        <v>8.476195577199585</v>
       </c>
       <c r="G88">
-        <v>-10.10210595274535</v>
+        <v>-11.82298216609456</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.688982422720444</v>
       </c>
       <c r="E89">
-        <v>-26.73161576274955</v>
+        <v>-27.14974446608799</v>
       </c>
       <c r="F89">
-        <v>7.107069933852562</v>
+        <v>8.125804449489422</v>
       </c>
       <c r="G89">
-        <v>-10.30009046344014</v>
+        <v>-11.71573277829163</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.709813607508106</v>
       </c>
       <c r="E90">
-        <v>-30.62832475615668</v>
+        <v>-30.14894033898835</v>
       </c>
       <c r="F90">
-        <v>7.137111506082488</v>
+        <v>8.489833818119275</v>
       </c>
       <c r="G90">
-        <v>-10.13538772479287</v>
+        <v>-11.17637122097976</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.719898645472933</v>
       </c>
       <c r="E91">
-        <v>-30.82597192989395</v>
+        <v>-31.17868132504935</v>
       </c>
       <c r="F91">
-        <v>7.398516093914317</v>
+        <v>8.600165729232947</v>
       </c>
       <c r="G91">
-        <v>-10.16174841292934</v>
+        <v>-11.29951873797028</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.70698184361451</v>
       </c>
       <c r="E92">
-        <v>-32.16338073429259</v>
+        <v>-32.48781921995988</v>
       </c>
       <c r="F92">
-        <v>6.190488029594131</v>
+        <v>8.227443473078115</v>
       </c>
       <c r="G92">
-        <v>-10.07117124008525</v>
+        <v>-11.77093827804302</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.669125494635647</v>
       </c>
       <c r="E93">
-        <v>-35.33565338273252</v>
+        <v>-34.75499083080258</v>
       </c>
       <c r="F93">
-        <v>6.781798219264891</v>
+        <v>8.183294803978512</v>
       </c>
       <c r="G93">
-        <v>-10.41900465807616</v>
+        <v>-11.47006954450164</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.594558800789143</v>
       </c>
       <c r="E94">
-        <v>-36.50599926158993</v>
+        <v>-36.90324561838713</v>
       </c>
       <c r="F94">
-        <v>6.546392770737327</v>
+        <v>8.185511515148404</v>
       </c>
       <c r="G94">
-        <v>-11.17350723416331</v>
+        <v>-11.25470139094693</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.482105906732008</v>
       </c>
       <c r="E95">
-        <v>-38.46804689603146</v>
+        <v>-39.75076621370475</v>
       </c>
       <c r="F95">
-        <v>6.656234288348542</v>
+        <v>8.295140970704502</v>
       </c>
       <c r="G95">
-        <v>-10.13763427051352</v>
+        <v>-11.41606629263446</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.326222002391028</v>
       </c>
       <c r="E96">
-        <v>-42.11269957074041</v>
+        <v>-40.42287832579609</v>
       </c>
       <c r="F96">
-        <v>6.308339859990417</v>
+        <v>8.365999518339972</v>
       </c>
       <c r="G96">
-        <v>-9.763525013585349</v>
+        <v>-11.29814157019847</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.129783123627599</v>
       </c>
       <c r="E97">
-        <v>-42.41047443970231</v>
+        <v>-44.52811383000588</v>
       </c>
       <c r="F97">
-        <v>6.376965129107939</v>
+        <v>7.941727958708927</v>
       </c>
       <c r="G97">
-        <v>-9.26718852713503</v>
+        <v>-10.82477310928847</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.895188532983042</v>
       </c>
       <c r="E98">
-        <v>-45.40594280543863</v>
+        <v>-46.59903789932778</v>
       </c>
       <c r="F98">
-        <v>6.314229552224321</v>
+        <v>7.933276954465566</v>
       </c>
       <c r="G98">
-        <v>-8.716698671003542</v>
+        <v>-11.45289215046441</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.632709353243098</v>
       </c>
       <c r="E99">
-        <v>-48.29066371459274</v>
+        <v>-48.19393542283748</v>
       </c>
       <c r="F99">
-        <v>6.205622302043277</v>
+        <v>8.007579853761875</v>
       </c>
       <c r="G99">
-        <v>-10.53312552564291</v>
+        <v>-11.09735181444054</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.349579319487821</v>
       </c>
       <c r="E100">
-        <v>-50.75925776826698</v>
+        <v>-50.42804228002039</v>
       </c>
       <c r="F100">
-        <v>6.042500193083999</v>
+        <v>7.410572153094661</v>
       </c>
       <c r="G100">
-        <v>-8.828297559295271</v>
+        <v>-10.68152024820179</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.071087307475426</v>
       </c>
       <c r="E101">
-        <v>-53.37439373032646</v>
+        <v>-53.35780684259793</v>
       </c>
       <c r="F101">
-        <v>5.88674558380522</v>
+        <v>7.2640256758654</v>
       </c>
       <c r="G101">
-        <v>-10.47330292408214</v>
+        <v>-10.89094373632253</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.794833321614076</v>
       </c>
       <c r="E102">
-        <v>-55.16275147140658</v>
+        <v>-56.20543542140999</v>
       </c>
       <c r="F102">
-        <v>4.930668778516114</v>
+        <v>7.123710178239998</v>
       </c>
       <c r="G102">
-        <v>-9.549513141845726</v>
+        <v>-10.93384740756059</v>
       </c>
     </row>
   </sheetData>
